--- a/artfynd/S 4467-2023 artfynd.xlsx
+++ b/artfynd/S 4467-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/497106</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/525890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1280,6 +1305,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820475</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820536</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820556</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1636,6 +1676,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66414473</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1760,6 +1805,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78593533</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1875,6 +1925,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84768865</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1990,6 +2045,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84768955</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2105,6 +2165,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84768978</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2214,6 +2279,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2321,6 +2391,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119281726</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2428,6 +2503,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119271741</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2529,6 +2609,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119278934</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2636,6 +2721,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119281822</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2742,6 +2832,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84768835</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119282518</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2985,6 +3085,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16028445</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3109,6 +3214,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117947303</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3228,6 +3338,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117951701</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3333,6 +3448,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16028446</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3440,6 +3560,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4628544</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3553,6 +3678,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110748385</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3649,6 +3779,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6820560</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3743,6 +3878,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110932370</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3851,6 +3991,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117947333</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3976,6 +4121,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/497103</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4091,6 +4241,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84768990</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4188,8 +4343,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4148680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>